--- a/SQExcel.Portal/src/content/docs/ja/docs/images/medium-scale/メインDB_2マスター(結合テスト用).xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/medium-scale/メインDB_2マスター(結合テスト用).xlsx
@@ -243,20 +243,20 @@
         <x:rFont val="Calibri"/>
         <x:family val="2"/>
       </x:rPr>
+      <x:t>ad_type</x:t>
+    </x:r>
+    <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Calibri"/>
+        <x:family val="2"/>
+      </x:rPr>
       <x:t>N</x:t>
-    </x:r>
-    <x:phoneticPr fontId="0"/>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>ad_type</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
   </x:si>
@@ -418,6 +418,20 @@
         <x:vertAlign val="baseline"/>
         <x:sz val="11"/>
         <x:color rgb="FF000000"/>
+        <x:rFont val="ＭＳ ゴシック"/>
+        <x:family val="2"/>
+        <x:charset val="128"/>
+      </x:rPr>
+      <x:t>アフィリエイト広告</x:t>
+    </x:r>
+    <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
         <x:family val="2"/>
       </x:rPr>
@@ -435,11 +449,127 @@
         <x:family val="2"/>
         <x:charset val="128"/>
       </x:rPr>
-      <x:t>アフィリエイト広告</x:t>
+      <x:t>ブロガーやメディア主が紹介し、実際に商品が売れたり申し込まれたりした時だけ費用が発生する仕組み</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
   </x:si>
   <x:si>
+    <x:t>sales.services</x:t>
+  </x:si>
+  <x:si>
+    <x:t>サービスマスター（広告種別・料金定義）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[INSERT] データ取り込み成功 処理件数：7件</x:t>
+  </x:si>
+  <x:si>
+    <x:t>service_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>service_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ad_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>banner_size</x:t>
+  </x:si>
+  <x:si>
+    <x:t>html_embed_available</x:t>
+  </x:si>
+  <x:si>
+    <x:t>js_embed_available</x:t>
+  </x:si>
+  <x:si>
+    <x:t>video_duration_sec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>price_weekly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>price_monthly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>currency_code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>is_active</x:t>
+  </x:si>
+  <x:si>
+    <x:t>サービスID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>サービス名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>広告種別（B=バナー広告,V=動画広告）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>バナーサイズ（バナー広告のみ。例:468x60,728x90,300x250）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTML埋め込み可否（バナー広告のみ）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JavaScript埋め込み可否（バナー広告のみ）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>動画表示時間（秒）（動画広告のみ）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>週単位料金（税抜）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>月単位料金（税抜）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>料金通貨コード（ISO 4217）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>有効フラグ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Char(8)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Char(1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decimal(15,2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Char(3)</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Calibri"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t>SNS0001</x:t>
+    </x:r>
+    <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Calibri"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t>SNS</x:t>
+    </x:r>
     <x:r>
       <x:rPr>
         <x:vertAlign val="baseline"/>
@@ -447,103 +577,12 @@
         <x:color rgb="FF000000"/>
         <x:rFont val="ＭＳ ゴシック"/>
         <x:family val="2"/>
-        <x:charset val="128"/>
-      </x:rPr>
-      <x:t>ブロガーやメディア主が紹介し、実際に商品が売れたり申し込まれたりした時だけ費用が発生する仕組み</x:t>
+      </x:rPr>
+      <x:t>-LINE広告</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
   </x:si>
   <x:si>
-    <x:t>sales.services</x:t>
-  </x:si>
-  <x:si>
-    <x:t>サービスマスター（広告種別・料金定義）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>service_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>service_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ad_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>banner_size</x:t>
-  </x:si>
-  <x:si>
-    <x:t>html_embed_available</x:t>
-  </x:si>
-  <x:si>
-    <x:t>js_embed_available</x:t>
-  </x:si>
-  <x:si>
-    <x:t>video_duration_sec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>price_weekly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>price_monthly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>currency_code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>is_active</x:t>
-  </x:si>
-  <x:si>
-    <x:t>サービスID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>サービス名</x:t>
-  </x:si>
-  <x:si>
-    <x:t>広告種別（B=バナー広告,V=動画広告）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>バナーサイズ（バナー広告のみ。例:468x60,728x90,300x250）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTML埋め込み可否（バナー広告のみ）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JavaScript埋め込み可否（バナー広告のみ）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>動画表示時間（秒）（動画広告のみ）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>週単位料金（税抜）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>月単位料金（税抜）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>料金通貨コード（ISO 4217）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>有効フラグ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Char(8)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Char(1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decimal(15,2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Char(3)</x:t>
-  </x:si>
-  <x:si>
     <x:r>
       <x:rPr>
         <x:vertAlign val="baseline"/>
@@ -552,7 +591,7 @@
         <x:rFont val="Calibri"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t>SNS0001</x:t>
+      <x:t>JPY</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
   </x:si>
@@ -565,6 +604,35 @@
         <x:rFont val="Calibri"/>
         <x:family val="2"/>
       </x:rPr>
+      <x:t>sys_operator</x:t>
+    </x:r>
+    <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Calibri"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t>SNS0002</x:t>
+    </x:r>
+    <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:t>TRUE</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Calibri"/>
+        <x:family val="2"/>
+      </x:rPr>
       <x:t>SNS</x:t>
     </x:r>
     <x:r>
@@ -575,69 +643,7 @@
         <x:rFont val="ＭＳ ゴシック"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t>-LINE広告</x:t>
-    </x:r>
-    <x:phoneticPr fontId="0"/>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>JPY</x:t>
-    </x:r>
-    <x:phoneticPr fontId="0"/>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>sys_operator</x:t>
-    </x:r>
-    <x:phoneticPr fontId="0"/>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>SNS</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="ＭＳ ゴシック"/>
-        <x:family val="2"/>
-      </x:rPr>
       <x:t>-INSTAGRAM広告</x:t>
-    </x:r>
-    <x:phoneticPr fontId="0"/>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:vertAlign val="baseline"/>
-        <x:sz val="11"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Calibri"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t>SNS0002</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
   </x:si>
@@ -816,10 +822,10 @@
     <x:phoneticPr fontId="0"/>
   </x:si>
   <x:si>
-    <x:t>[INSERT] データ取り込み成功 処理件数：7件</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUE</x:t>
+    <x:t>Microsoft SQL Server</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DB種類</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -911,7 +917,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
@@ -988,8 +994,14 @@
     <x:xf numFmtId="2" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="54">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <x:alignment vertical="top"/>
@@ -1177,6 +1189,14 @@
     <x:xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="0" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1522,8 +1542,9 @@
     <x:col min="1" max="1" width="18.726562" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="18.726562" style="2" customWidth="1"/>
-    <x:col min="4" max="5" width="50.726562" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="22.726562" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="50.726562" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="3" customWidth="1"/>
     <x:col min="7" max="7" width="30.726562" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="22.726562" style="3" customWidth="1"/>
     <x:col min="9" max="9" width="30.726562" style="2" customWidth="1"/>
@@ -1532,7 +1553,7 @@
     <x:col min="12" max="16384" width="9.179688" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A1" s="32" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1545,13 +1566,17 @@
       <x:c r="D1" s="33" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="9"/>
-      <x:c r="F1" s="8"/>
+      <x:c r="E1" s="34" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F1" s="52" t="s">
+        <x:v>95</x:v>
+      </x:c>
       <x:c r="G1" s="9"/>
       <x:c r="H1" s="8"/>
       <x:c r="I1" s="9"/>
     </x:row>
-    <x:row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="2" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A2" s="32" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -1564,7 +1589,7 @@
       <x:c r="H2" s="8"/>
       <x:c r="I2" s="9"/>
     </x:row>
-    <x:row r="3" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="3" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A3" s="35" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1599,7 +1624,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="4" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A4" s="35" t="s">
         <x:v>16</x:v>
       </x:c>
@@ -1630,7 +1655,7 @@
       <x:c r="J4" s="41"/>
       <x:c r="K4" s="41"/>
     </x:row>
-    <x:row r="5" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="5" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A5" s="35" t="s">
         <x:v>25</x:v>
       </x:c>
@@ -1661,7 +1686,7 @@
       <x:c r="J5" s="41"/>
       <x:c r="K5" s="41"/>
     </x:row>
-    <x:row r="6" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="6" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A6" s="32" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -1692,7 +1717,7 @@
       <x:c r="J6" s="41"/>
       <x:c r="K6" s="41"/>
     </x:row>
-    <x:row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <x:row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <x:c r="A7" s="42" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -1719,12 +1744,12 @@
       <x:c r="J7" s="46"/>
       <x:c r="K7" s="46"/>
     </x:row>
-    <x:row r="8" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <x:row r="8" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B8" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
         <x:v>41</x:v>
@@ -1743,15 +1768,15 @@
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:12" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+    <x:row r="9" spans="1:11" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B9" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="31" t="s">
         <x:v>45</x:v>
@@ -1764,7 +1789,7 @@
       </x:c>
       <x:c r="J9" s="29"/>
     </x:row>
-    <x:row r="10" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <x:row r="10" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="J10" s="29"/>
     </x:row>
   </x:sheetData>
@@ -1811,8 +1836,9 @@
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="42.179688" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="16.726562" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="28.726562" style="2" customWidth="1"/>
-    <x:col min="6" max="8" width="14.726562" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="1" customWidth="1"/>
+    <x:col min="7" max="8" width="14.726562" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="24.363281" style="24" customWidth="1"/>
     <x:col min="10" max="10" width="26.269531" style="24" customWidth="1"/>
     <x:col min="11" max="11" width="16.726562" style="2" customWidth="1"/>
@@ -1826,7 +1852,7 @@
     <x:col min="19" max="16384" width="9.179688" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="1" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A1" s="32" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1839,7 +1865,12 @@
       <x:c r="D1" s="33" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E1" s="9"/>
+      <x:c r="E1" s="34" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F1" s="53" t="s">
+        <x:v>95</x:v>
+      </x:c>
       <x:c r="I1" s="25"/>
       <x:c r="J1" s="25"/>
       <x:c r="K1" s="9"/>
@@ -1848,12 +1879,12 @@
       <x:c r="O1" s="8"/>
       <x:c r="P1" s="9"/>
     </x:row>
-    <x:row r="2" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="2" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A2" s="32" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
@@ -1866,42 +1897,42 @@
       <x:c r="O2" s="8"/>
       <x:c r="P2" s="9"/>
     </x:row>
-    <x:row r="3" spans="1:19" ht="29" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="3" spans="1:18" ht="29" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A3" s="35" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="36" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C3" s="37" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D3" s="37" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E3" s="37" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F3" s="47" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G3" s="47" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H3" s="47" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I3" s="48" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J3" s="48" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K3" s="37" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L3" s="47" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M3" s="38" t="s">
         <x:v>10</x:v>
@@ -1922,42 +1953,42 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="4" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A4" s="35" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="36" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C4" s="37" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D4" s="37" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E4" s="37" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F4" s="41" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G4" s="41" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H4" s="41" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I4" s="49" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J4" s="49" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K4" s="37" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L4" s="41" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="M4" s="40" t="s">
         <x:v>21</x:v>
@@ -1974,42 +2005,42 @@
       <x:c r="Q4" s="41"/>
       <x:c r="R4" s="41"/>
     </x:row>
-    <x:row r="5" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="5" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A5" s="35" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="36" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C5" s="37" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="37" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E5" s="37" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="47" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G5" s="47" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H5" s="47" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I5" s="48" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J5" s="48" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K5" s="37" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="L5" s="47" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="I5" s="48" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="J5" s="48" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="K5" s="37" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L5" s="47" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="M5" s="38" t="s">
         <x:v>29</x:v>
@@ -2026,7 +2057,7 @@
       <x:c r="Q5" s="41"/>
       <x:c r="R5" s="41"/>
     </x:row>
-    <x:row r="6" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="6" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A6" s="32" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -2078,7 +2109,7 @@
       <x:c r="Q6" s="41"/>
       <x:c r="R6" s="41"/>
     </x:row>
-    <x:row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="A7" s="42" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -2126,15 +2157,15 @@
       <x:c r="Q7" s="46"/>
       <x:c r="R7" s="46"/>
     </x:row>
-    <x:row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B8" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>0</x:v>
@@ -2149,33 +2180,33 @@
         <x:v>600000</x:v>
       </x:c>
       <x:c r="K8" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L8" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N8" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P8" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q8" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R8" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B9" s="2" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>0</x:v>
@@ -2190,33 +2221,33 @@
         <x:v>600000</x:v>
       </x:c>
       <x:c r="K9" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L9" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N9" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P9" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q9" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R9" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B10" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>0</x:v>
@@ -2231,33 +2262,33 @@
         <x:v>600000</x:v>
       </x:c>
       <x:c r="K10" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L10" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N10" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P10" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q10" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B11" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>0</x:v>
@@ -2272,33 +2303,33 @@
         <x:v>600000</x:v>
       </x:c>
       <x:c r="K11" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L11" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N11" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P11" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q11" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R11" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B12" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C12" s="31" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>1</x:v>
@@ -2313,33 +2344,33 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="K12" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L12" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N12" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P12" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q12" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R12" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B13" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="31" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>1</x:v>
@@ -2354,33 +2385,33 @@
         <x:v>70000</x:v>
       </x:c>
       <x:c r="K13" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L13" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N13" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P13" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q13" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R13" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B14" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C14" s="31" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>1</x:v>
@@ -2395,19 +2426,19 @@
         <x:v>100000</x:v>
       </x:c>
       <x:c r="K14" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L14" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N14" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P14" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q14" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R14" s="1" t="s">
         <x:v>33</x:v>
